--- a/spec/fixtures/files/valid_import.xlsx
+++ b/spec/fixtures/files/valid_import.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+<worksheet space="preserve">
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -337,36 +337,36 @@
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
           <t>email</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>full_name</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
+          <t>Frank Example</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
           <t>frank@example.com</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>Frank Example</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
+          <t>Grace Example</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
           <t>grace@example.com</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>Grace Example</t>
         </is>
       </c>
     </row>
